--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D727505-5690-4F83-9538-7FEEF5E42DE8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5A2849-DE67-480A-8759-58E0561159F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="97">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -325,6 +325,9 @@
   </si>
   <si>
     <t>Today I fixed a laptop It was intersting task</t>
+  </si>
+  <si>
+    <t>I am have to focus on study rather than games</t>
   </si>
 </sst>
 </file>
@@ -2718,26 +2721,50 @@
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="14"/>
-      <c r="C41" s="14"/>
-      <c r="D41" s="14"/>
-      <c r="E41" s="14"/>
-      <c r="F41" s="14"/>
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15" t="str">
+      <c r="A41" s="13">
+        <v>46278</v>
+      </c>
+      <c r="B41" s="14">
+        <v>300</v>
+      </c>
+      <c r="C41" s="14">
+        <v>0</v>
+      </c>
+      <c r="D41" s="14">
+        <v>120</v>
+      </c>
+      <c r="E41" s="14">
+        <v>0</v>
+      </c>
+      <c r="F41" s="14">
+        <v>0</v>
+      </c>
+      <c r="G41" s="14">
+        <v>0</v>
+      </c>
+      <c r="H41" s="14">
+        <v>240</v>
+      </c>
+      <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J41" s="15" t="str">
+        <v>660</v>
+      </c>
+      <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K41" s="16"/>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="17"/>
+        <v>780</v>
+      </c>
+      <c r="K41" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L41" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M41" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N41" s="17" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A42" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C5A2849-DE67-480A-8759-58E0561159F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E68E0BB-1603-4782-BF12-BD5D95A27495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="98">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -328,6 +328,9 @@
   </si>
   <si>
     <t>I am have to focus on study rather than games</t>
+  </si>
+  <si>
+    <t>I tried to focus on study rather than games and I didn't play instead I did coding and study today but still I have to study more</t>
   </si>
 </sst>
 </file>
@@ -2766,27 +2769,51 @@
         <v>96</v>
       </c>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15" t="str">
+    <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A42" s="13">
+        <v>46279</v>
+      </c>
+      <c r="B42" s="14">
+        <v>480</v>
+      </c>
+      <c r="C42" s="14">
+        <v>0</v>
+      </c>
+      <c r="D42" s="14">
+        <v>150</v>
+      </c>
+      <c r="E42" s="14">
+        <v>60</v>
+      </c>
+      <c r="F42" s="14">
+        <v>100</v>
+      </c>
+      <c r="G42" s="14">
+        <v>2</v>
+      </c>
+      <c r="H42" s="14">
+        <v>120</v>
+      </c>
+      <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J42" s="15" t="str">
+        <v>910</v>
+      </c>
+      <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K42" s="16"/>
-      <c r="L42" s="16"/>
-      <c r="M42" s="16"/>
-      <c r="N42" s="17"/>
+        <v>530</v>
+      </c>
+      <c r="K42" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L42" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M42" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N42" s="17" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A43" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E68E0BB-1603-4782-BF12-BD5D95A27495}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACC94FA-9091-4908-AA31-2664F3A334F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="99">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -331,6 +331,9 @@
   </si>
   <si>
     <t>I tried to focus on study rather than games and I didn't play instead I did coding and study today but still I have to study more</t>
+  </si>
+  <si>
+    <t>Today I had CA of python, And I am tired today little bit sleep issue I guess again</t>
   </si>
 </sst>
 </file>
@@ -2815,27 +2818,51 @@
         <v>97</v>
       </c>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="14"/>
-      <c r="E43" s="14"/>
-      <c r="F43" s="14"/>
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15" t="str">
+    <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A43" s="13">
+        <v>46280</v>
+      </c>
+      <c r="B43" s="14">
+        <v>300</v>
+      </c>
+      <c r="C43" s="14">
+        <v>0</v>
+      </c>
+      <c r="D43" s="14">
+        <v>120</v>
+      </c>
+      <c r="E43" s="14">
+        <v>60</v>
+      </c>
+      <c r="F43" s="14">
+        <v>200</v>
+      </c>
+      <c r="G43" s="14">
+        <v>4</v>
+      </c>
+      <c r="H43" s="14">
+        <v>120</v>
+      </c>
+      <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J43" s="15" t="str">
+        <v>800</v>
+      </c>
+      <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="16"/>
-      <c r="M43" s="16"/>
-      <c r="N43" s="17"/>
+        <v>640</v>
+      </c>
+      <c r="K43" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L43" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M43" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N43" s="17" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A44" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1ACC94FA-9091-4908-AA31-2664F3A334F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0592B033-4260-4295-8D65-5AFFB5B516BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="100">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -334,6 +334,9 @@
   </si>
   <si>
     <t>Today I had CA of python, And I am tired today little bit sleep issue I guess again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Today I felt good because I get good marks in CA of Python and Networking according to me and also my eyes were hearting today because of dryness I think so classes didn't go well </t>
   </si>
 </sst>
 </file>
@@ -2864,27 +2867,51 @@
         <v>98</v>
       </c>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A44" s="13"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="14"/>
-      <c r="E44" s="14"/>
-      <c r="F44" s="14"/>
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15" t="str">
+    <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="13">
+        <v>46281</v>
+      </c>
+      <c r="B44" s="14">
+        <v>420</v>
+      </c>
+      <c r="C44" s="14">
+        <v>0</v>
+      </c>
+      <c r="D44" s="14">
+        <v>180</v>
+      </c>
+      <c r="E44" s="14">
+        <v>0</v>
+      </c>
+      <c r="F44" s="14">
+        <v>400</v>
+      </c>
+      <c r="G44" s="14">
+        <v>8</v>
+      </c>
+      <c r="H44" s="14">
+        <v>60</v>
+      </c>
+      <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J44" s="15" t="str">
+        <v>1060</v>
+      </c>
+      <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K44" s="16"/>
-      <c r="L44" s="16"/>
-      <c r="M44" s="16"/>
-      <c r="N44" s="17"/>
+        <v>380</v>
+      </c>
+      <c r="K44" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L44" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N44" s="17" t="s">
+        <v>99</v>
+      </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A45" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0592B033-4260-4295-8D65-5AFFB5B516BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAD562E-F1C5-4A93-BDD6-E4D015A4219C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="101">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -337,6 +337,9 @@
   </si>
   <si>
     <t xml:space="preserve">Today I felt good because I get good marks in CA of Python and Networking according to me and also my eyes were hearting today because of dryness I think so classes didn't go well </t>
+  </si>
+  <si>
+    <t>Analytical Skills CA is coming I don't know what to study</t>
   </si>
 </sst>
 </file>
@@ -1504,7 +1507,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G14" s="14">
         <v>5</v>
@@ -1514,11 +1517,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>780</v>
+        <v>730</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>710</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>56</v>
@@ -1964,7 +1967,7 @@
         <v>60</v>
       </c>
       <c r="F24" s="14">
-        <v>300</v>
+        <v>250</v>
       </c>
       <c r="G24" s="14">
         <v>5</v>
@@ -1974,11 +1977,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1030</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>77</v>
@@ -2914,26 +2917,50 @@
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A45" s="13"/>
-      <c r="B45" s="14"/>
-      <c r="C45" s="14"/>
-      <c r="D45" s="14"/>
-      <c r="E45" s="14"/>
-      <c r="F45" s="14"/>
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15" t="str">
+      <c r="A45" s="13">
+        <v>46282</v>
+      </c>
+      <c r="B45" s="14">
+        <v>420</v>
+      </c>
+      <c r="C45" s="14">
+        <v>0</v>
+      </c>
+      <c r="D45" s="14">
+        <v>150</v>
+      </c>
+      <c r="E45" s="14">
+        <v>0</v>
+      </c>
+      <c r="F45" s="14">
+        <v>250</v>
+      </c>
+      <c r="G45" s="14">
+        <v>5</v>
+      </c>
+      <c r="H45" s="14">
+        <v>120</v>
+      </c>
+      <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J45" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K45" s="16"/>
-      <c r="L45" s="16"/>
-      <c r="M45" s="16"/>
-      <c r="N45" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K45" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L45" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M45" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N45" s="17" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A46" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAD562E-F1C5-4A93-BDD6-E4D015A4219C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D46A40-2EB3-45E3-B9AB-E182BF7933D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="102">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -340,6 +340,9 @@
   </si>
   <si>
     <t>Analytical Skills CA is coming I don't know what to study</t>
+  </si>
+  <si>
+    <t>I studied analytical skills subject too much today</t>
   </si>
 </sst>
 </file>
@@ -2927,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="14">
-        <v>150</v>
+        <v>210</v>
       </c>
       <c r="E45" s="14">
         <v>0</v>
@@ -2943,11 +2946,11 @@
       </c>
       <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v>940</v>
+        <v>1000</v>
       </c>
       <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>440</v>
       </c>
       <c r="K45" s="16" t="s">
         <v>49</v>
@@ -2963,26 +2966,50 @@
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A46" s="13"/>
-      <c r="B46" s="14"/>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15" t="str">
+      <c r="A46" s="13">
+        <v>46283</v>
+      </c>
+      <c r="B46" s="14">
+        <v>420</v>
+      </c>
+      <c r="C46" s="14">
+        <v>0</v>
+      </c>
+      <c r="D46" s="14">
+        <v>300</v>
+      </c>
+      <c r="E46" s="14">
+        <v>0</v>
+      </c>
+      <c r="F46" s="14">
+        <v>300</v>
+      </c>
+      <c r="G46" s="14">
+        <v>6</v>
+      </c>
+      <c r="H46" s="14">
+        <v>60</v>
+      </c>
+      <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J46" s="15" t="str">
+        <v>1080</v>
+      </c>
+      <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K46" s="16"/>
-      <c r="L46" s="16"/>
-      <c r="M46" s="16"/>
-      <c r="N46" s="17"/>
+        <v>360</v>
+      </c>
+      <c r="K46" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L46" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M46" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N46" s="17" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A47" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24D46A40-2EB3-45E3-B9AB-E182BF7933D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B5DDC6-09FB-4BB6-964B-5311E40C583E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="103">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>I studied analytical skills subject too much today</t>
+  </si>
+  <si>
+    <t>Today was the worst day so far. I had a bad CA in Analytical Skills.</t>
   </si>
 </sst>
 </file>
@@ -3012,26 +3015,50 @@
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A47" s="13"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15" t="str">
+      <c r="A47" s="13">
+        <v>46284</v>
+      </c>
+      <c r="B47" s="14">
+        <v>420</v>
+      </c>
+      <c r="C47" s="14">
+        <v>0</v>
+      </c>
+      <c r="D47" s="14">
+        <v>60</v>
+      </c>
+      <c r="E47" s="14">
+        <v>0</v>
+      </c>
+      <c r="F47" s="14">
+        <v>50</v>
+      </c>
+      <c r="G47" s="14">
+        <v>1</v>
+      </c>
+      <c r="H47" s="14">
+        <v>300</v>
+      </c>
+      <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J47" s="15" t="str">
+        <v>830</v>
+      </c>
+      <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K47" s="16"/>
-      <c r="L47" s="16"/>
-      <c r="M47" s="16"/>
-      <c r="N47" s="17"/>
+        <v>610</v>
+      </c>
+      <c r="K47" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L47" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M47" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N47" s="17" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A48" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72B5DDC6-09FB-4BB6-964B-5311E40C583E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F00AAA4-36B8-4342-A53A-64027D4D2696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="104">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -346,6 +346,9 @@
   </si>
   <si>
     <t>Today was the worst day so far. I had a bad CA in Analytical Skills.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Just normal day, I completed some DBMS notes </t>
   </si>
 </sst>
 </file>
@@ -3061,26 +3064,50 @@
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A48" s="13"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15" t="str">
+      <c r="A48" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B48" s="14">
+        <v>300</v>
+      </c>
+      <c r="C48" s="14">
+        <v>0</v>
+      </c>
+      <c r="D48" s="14">
+        <v>300</v>
+      </c>
+      <c r="E48" s="14">
+        <v>0</v>
+      </c>
+      <c r="F48" s="14">
+        <v>0</v>
+      </c>
+      <c r="G48" s="14">
+        <v>0</v>
+      </c>
+      <c r="H48" s="14">
+        <v>240</v>
+      </c>
+      <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J48" s="15" t="str">
+        <v>840</v>
+      </c>
+      <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K48" s="16"/>
-      <c r="L48" s="16"/>
-      <c r="M48" s="16"/>
-      <c r="N48" s="17"/>
+        <v>600</v>
+      </c>
+      <c r="K48" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="L48" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M48" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N48" s="17" t="s">
+        <v>103</v>
+      </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A49" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F00AAA4-36B8-4342-A53A-64027D4D2696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC6A405-78B7-4A52-AB37-F8511E3AD56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="106">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -349,6 +349,12 @@
   </si>
   <si>
     <t xml:space="preserve">Just normal day, I completed some DBMS notes </t>
+  </si>
+  <si>
+    <t>Very Satisfied</t>
+  </si>
+  <si>
+    <t>Did some DBMS notes and networking notes and Practical</t>
   </si>
 </sst>
 </file>
@@ -3110,26 +3116,50 @@
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="13"/>
-      <c r="B49" s="14"/>
-      <c r="C49" s="14"/>
-      <c r="D49" s="14"/>
-      <c r="E49" s="14"/>
-      <c r="F49" s="14"/>
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15" t="str">
+      <c r="A49" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B49" s="14">
+        <v>360</v>
+      </c>
+      <c r="C49" s="14">
+        <v>0</v>
+      </c>
+      <c r="D49" s="14">
+        <v>380</v>
+      </c>
+      <c r="E49" s="14">
+        <v>40</v>
+      </c>
+      <c r="F49" s="14">
+        <v>100</v>
+      </c>
+      <c r="G49" s="14">
+        <v>2</v>
+      </c>
+      <c r="H49" s="14">
+        <v>60</v>
+      </c>
+      <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J49" s="15" t="str">
+        <v>940</v>
+      </c>
+      <c r="J49" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K49" s="16"/>
-      <c r="L49" s="16"/>
-      <c r="M49" s="16"/>
-      <c r="N49" s="17"/>
+        <v>500</v>
+      </c>
+      <c r="K49" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L49" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N49" s="17" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A50" s="13"/>
@@ -3144,10 +3174,7 @@
         <f t="shared" si="0"/>
         <v/>
       </c>
-      <c r="J50" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
+      <c r="J50" s="15"/>
       <c r="K50" s="16"/>
       <c r="L50" s="16"/>
       <c r="M50" s="16"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DC6A405-78B7-4A52-AB37-F8511E3AD56B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B29E233-6013-4BF3-B866-5992EE78FC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -355,6 +355,9 @@
   </si>
   <si>
     <t>Did some DBMS notes and networking notes and Practical</t>
+  </si>
+  <si>
+    <t>Again I am having speeling issues now it has been 3 days since I slept properly</t>
   </si>
 </sst>
 </file>
@@ -3145,7 +3148,7 @@
         <v>940</v>
       </c>
       <c r="J49" s="15">
-        <f t="shared" si="1"/>
+        <f>IF(I49="","",1440-I49)</f>
         <v>500</v>
       </c>
       <c r="K49" s="16" t="s">
@@ -3161,24 +3164,51 @@
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="13">
+        <v>46287</v>
+      </c>
+      <c r="B50" s="14">
+        <v>240</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>60</v>
+      </c>
+      <c r="E50" s="14">
+        <v>150</v>
+      </c>
+      <c r="F50" s="14">
+        <v>250</v>
+      </c>
+      <c r="G50" s="14">
+        <v>5</v>
+      </c>
+      <c r="H50" s="14">
+        <v>120</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15"/>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>820</v>
+      </c>
+      <c r="J50" s="15">
+        <f>IF(I50="","",1440-I50)</f>
+        <v>620</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>69</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>
@@ -3194,7 +3224,7 @@
         <v/>
       </c>
       <c r="J51" s="15" t="str">
-        <f t="shared" si="1"/>
+        <f>IF(I51="","",1440-I51)</f>
         <v/>
       </c>
       <c r="K51" s="16"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B29E233-6013-4BF3-B866-5992EE78FC46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A13F033-E40A-4989-B624-2EE2014CBF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>Again I am having speeling issues now it has been 3 days since I slept properly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I haven’t been sleeping well lately, so I feel sleepy in class. Feeling so low </t>
   </si>
 </sst>
 </file>
@@ -3210,27 +3213,51 @@
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="13">
+        <v>46288</v>
+      </c>
+      <c r="B51" s="14">
+        <v>300</v>
+      </c>
+      <c r="C51" s="14">
+        <v>0</v>
+      </c>
+      <c r="D51" s="14">
+        <v>150</v>
+      </c>
+      <c r="E51" s="14">
+        <v>60</v>
+      </c>
+      <c r="F51" s="14">
+        <v>400</v>
+      </c>
+      <c r="G51" s="14">
+        <v>8</v>
+      </c>
+      <c r="H51" s="14">
+        <v>120</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>1030</v>
+      </c>
+      <c r="J51" s="15">
         <f>IF(I51="","",1440-I51)</f>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>410</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A13F033-E40A-4989-B624-2EE2014CBF7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138E5062-994B-451F-A863-6A1B82B1253B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="109">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -361,6 +361,9 @@
   </si>
   <si>
     <t xml:space="preserve">I haven’t been sleeping well lately, so I feel sleepy in class. Feeling so low </t>
+  </si>
+  <si>
+    <t>I have been completing my Python CA2, with my friends</t>
   </si>
 </sst>
 </file>
@@ -1197,7 +1200,7 @@
         <v>330</v>
       </c>
       <c r="C7" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D7" s="14">
         <v>120</v>
@@ -1216,11 +1219,11 @@
       </c>
       <c r="I7" s="15">
         <f t="shared" si="0"/>
-        <v>810</v>
+        <v>840</v>
       </c>
       <c r="J7" s="15">
         <f t="shared" si="1"/>
-        <v>630</v>
+        <v>600</v>
       </c>
       <c r="K7" s="16" t="s">
         <v>49</v>
@@ -1243,7 +1246,7 @@
         <v>440</v>
       </c>
       <c r="C8" s="14">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="D8" s="14">
         <v>20</v>
@@ -1262,11 +1265,11 @@
       </c>
       <c r="I8" s="15">
         <f t="shared" si="0"/>
-        <v>895</v>
+        <v>915</v>
       </c>
       <c r="J8" s="15">
         <f t="shared" si="1"/>
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="K8" s="16" t="s">
         <v>58</v>
@@ -1289,7 +1292,7 @@
         <v>440</v>
       </c>
       <c r="C9" s="14">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="D9" s="14">
         <v>120</v>
@@ -1308,11 +1311,11 @@
       </c>
       <c r="I9" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="J9" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>340</v>
       </c>
       <c r="K9" s="16" t="s">
         <v>49</v>
@@ -1335,7 +1338,7 @@
         <v>430</v>
       </c>
       <c r="C10" s="14">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="D10" s="14">
         <v>150</v>
@@ -1354,11 +1357,11 @@
       </c>
       <c r="I10" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1080</v>
       </c>
       <c r="J10" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>360</v>
       </c>
       <c r="K10" s="16" t="s">
         <v>49</v>
@@ -1381,7 +1384,7 @@
         <v>360</v>
       </c>
       <c r="C11" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D11" s="14">
         <v>300</v>
@@ -1400,11 +1403,11 @@
       </c>
       <c r="I11" s="15">
         <f t="shared" si="0"/>
-        <v>930</v>
+        <v>990</v>
       </c>
       <c r="J11" s="15">
         <f t="shared" si="1"/>
-        <v>510</v>
+        <v>450</v>
       </c>
       <c r="K11" s="16" t="s">
         <v>56</v>
@@ -1427,7 +1430,7 @@
         <v>440</v>
       </c>
       <c r="C12" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D12" s="14">
         <v>300</v>
@@ -1446,11 +1449,11 @@
       </c>
       <c r="I12" s="15">
         <f t="shared" si="0"/>
-        <v>1040</v>
+        <v>1060</v>
       </c>
       <c r="J12" s="15">
         <f t="shared" si="1"/>
-        <v>400</v>
+        <v>380</v>
       </c>
       <c r="K12" s="16" t="s">
         <v>49</v>
@@ -1473,7 +1476,7 @@
         <v>440</v>
       </c>
       <c r="C13" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D13" s="14">
         <v>0</v>
@@ -1492,11 +1495,11 @@
       </c>
       <c r="I13" s="15">
         <f t="shared" si="0"/>
-        <v>940</v>
+        <v>970</v>
       </c>
       <c r="J13" s="15">
         <f t="shared" si="1"/>
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="K13" s="16" t="s">
         <v>49</v>
@@ -1519,7 +1522,7 @@
         <v>300</v>
       </c>
       <c r="C14" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D14" s="14">
         <v>60</v>
@@ -1538,11 +1541,11 @@
       </c>
       <c r="I14" s="15">
         <f t="shared" si="0"/>
-        <v>730</v>
+        <v>780</v>
       </c>
       <c r="J14" s="15">
         <f t="shared" si="1"/>
-        <v>710</v>
+        <v>660</v>
       </c>
       <c r="K14" s="16" t="s">
         <v>56</v>
@@ -1611,7 +1614,7 @@
         <v>240</v>
       </c>
       <c r="C16" s="14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D16" s="14">
         <v>180</v>
@@ -1630,11 +1633,11 @@
       </c>
       <c r="I16" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>1030</v>
       </c>
       <c r="J16" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="K16" s="16" t="s">
         <v>58</v>
@@ -1657,7 +1660,7 @@
         <v>450</v>
       </c>
       <c r="C17" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D17" s="14">
         <v>140</v>
@@ -1676,11 +1679,11 @@
       </c>
       <c r="I17" s="15">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>940</v>
       </c>
       <c r="J17" s="15">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>500</v>
       </c>
       <c r="K17" s="16" t="s">
         <v>49</v>
@@ -1703,7 +1706,7 @@
         <v>420</v>
       </c>
       <c r="C18" s="14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D18" s="14">
         <v>240</v>
@@ -1722,11 +1725,11 @@
       </c>
       <c r="I18" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1005</v>
       </c>
       <c r="J18" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>435</v>
       </c>
       <c r="K18" s="16" t="s">
         <v>49</v>
@@ -1749,7 +1752,7 @@
         <v>300</v>
       </c>
       <c r="C19" s="14">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="D19" s="14">
         <v>390</v>
@@ -1768,11 +1771,11 @@
       </c>
       <c r="I19" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>920</v>
       </c>
       <c r="J19" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="K19" s="16" t="s">
         <v>49</v>
@@ -1795,7 +1798,7 @@
         <v>440</v>
       </c>
       <c r="C20" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D20" s="14">
         <v>120</v>
@@ -1814,11 +1817,11 @@
       </c>
       <c r="I20" s="15">
         <f t="shared" si="0"/>
-        <v>860</v>
+        <v>890</v>
       </c>
       <c r="J20" s="15">
         <f t="shared" si="1"/>
-        <v>580</v>
+        <v>550</v>
       </c>
       <c r="K20" s="16" t="s">
         <v>49</v>
@@ -1841,7 +1844,7 @@
         <v>420</v>
       </c>
       <c r="C21" s="14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D21" s="14">
         <v>240</v>
@@ -1860,11 +1863,11 @@
       </c>
       <c r="I21" s="15">
         <f t="shared" si="0"/>
-        <v>1020</v>
+        <v>1065</v>
       </c>
       <c r="J21" s="15">
         <f t="shared" si="1"/>
-        <v>420</v>
+        <v>375</v>
       </c>
       <c r="K21" s="16" t="s">
         <v>49</v>
@@ -1887,7 +1890,7 @@
         <v>300</v>
       </c>
       <c r="C22" s="14">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="D22" s="14">
         <v>200</v>
@@ -1906,11 +1909,11 @@
       </c>
       <c r="I22" s="15">
         <f t="shared" si="0"/>
-        <v>900</v>
+        <v>955</v>
       </c>
       <c r="J22" s="15">
         <f t="shared" si="1"/>
-        <v>540</v>
+        <v>485</v>
       </c>
       <c r="K22" s="16" t="s">
         <v>56</v>
@@ -1979,7 +1982,7 @@
         <v>360</v>
       </c>
       <c r="C24" s="14">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D24" s="14">
         <v>300</v>
@@ -1998,11 +2001,11 @@
       </c>
       <c r="I24" s="15">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>1105</v>
       </c>
       <c r="J24" s="15">
         <f t="shared" si="1"/>
-        <v>410</v>
+        <v>335</v>
       </c>
       <c r="K24" s="16" t="s">
         <v>77</v>
@@ -2025,7 +2028,7 @@
         <v>360</v>
       </c>
       <c r="C25" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D25" s="14">
         <v>0</v>
@@ -2044,11 +2047,11 @@
       </c>
       <c r="I25" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>900</v>
       </c>
       <c r="J25" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>540</v>
       </c>
       <c r="K25" s="16" t="s">
         <v>49</v>
@@ -2071,7 +2074,7 @@
         <v>420</v>
       </c>
       <c r="C26" s="14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D26" s="14">
         <v>120</v>
@@ -2090,11 +2093,11 @@
       </c>
       <c r="I26" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>935</v>
       </c>
       <c r="J26" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>505</v>
       </c>
       <c r="K26" s="16" t="s">
         <v>77</v>
@@ -2117,7 +2120,7 @@
         <v>420</v>
       </c>
       <c r="C27" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D27" s="14">
         <v>300</v>
@@ -2136,11 +2139,11 @@
       </c>
       <c r="I27" s="15">
         <f t="shared" si="0"/>
-        <v>870</v>
+        <v>900</v>
       </c>
       <c r="J27" s="15">
         <f t="shared" si="1"/>
-        <v>570</v>
+        <v>540</v>
       </c>
       <c r="K27" s="16" t="s">
         <v>49</v>
@@ -2163,7 +2166,7 @@
         <v>400</v>
       </c>
       <c r="C28" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D28" s="14">
         <v>60</v>
@@ -2182,11 +2185,11 @@
       </c>
       <c r="I28" s="15">
         <f t="shared" si="0"/>
-        <v>890</v>
+        <v>920</v>
       </c>
       <c r="J28" s="15">
         <f t="shared" si="1"/>
-        <v>550</v>
+        <v>520</v>
       </c>
       <c r="K28" s="16" t="s">
         <v>56</v>
@@ -2209,7 +2212,7 @@
         <v>300</v>
       </c>
       <c r="C29" s="14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D29" s="14">
         <v>120</v>
@@ -2228,11 +2231,11 @@
       </c>
       <c r="I29" s="15">
         <f t="shared" si="0"/>
-        <v>780</v>
+        <v>850</v>
       </c>
       <c r="J29" s="15">
         <f t="shared" si="1"/>
-        <v>660</v>
+        <v>590</v>
       </c>
       <c r="K29" s="16" t="s">
         <v>49</v>
@@ -2255,7 +2258,7 @@
         <v>320</v>
       </c>
       <c r="C30" s="14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D30" s="14">
         <v>30</v>
@@ -2274,11 +2277,11 @@
       </c>
       <c r="I30" s="15">
         <f t="shared" si="0"/>
-        <v>950</v>
+        <v>1030</v>
       </c>
       <c r="J30" s="15">
         <f t="shared" si="1"/>
-        <v>490</v>
+        <v>410</v>
       </c>
       <c r="K30" s="16" t="s">
         <v>56</v>
@@ -2301,7 +2304,7 @@
         <v>450</v>
       </c>
       <c r="C31" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D31" s="14">
         <v>240</v>
@@ -2320,11 +2323,11 @@
       </c>
       <c r="I31" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>1010</v>
       </c>
       <c r="J31" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>430</v>
       </c>
       <c r="K31" s="16" t="s">
         <v>49</v>
@@ -2347,7 +2350,7 @@
         <v>360</v>
       </c>
       <c r="C32" s="14">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="D32" s="14">
         <v>240</v>
@@ -2366,11 +2369,11 @@
       </c>
       <c r="I32" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1120</v>
       </c>
       <c r="J32" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>320</v>
       </c>
       <c r="K32" s="16" t="s">
         <v>56</v>
@@ -2393,7 +2396,7 @@
         <v>450</v>
       </c>
       <c r="C33" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D33" s="14">
         <v>300</v>
@@ -2412,11 +2415,11 @@
       </c>
       <c r="I33" s="15">
         <f t="shared" si="0"/>
-        <v>960</v>
+        <v>980</v>
       </c>
       <c r="J33" s="15">
         <f t="shared" si="1"/>
-        <v>480</v>
+        <v>460</v>
       </c>
       <c r="K33" s="16" t="s">
         <v>58</v>
@@ -2439,7 +2442,7 @@
         <v>720</v>
       </c>
       <c r="C34" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D34" s="14">
         <v>30</v>
@@ -2458,11 +2461,11 @@
       </c>
       <c r="I34" s="15">
         <f t="shared" si="0"/>
-        <v>990</v>
+        <v>1015</v>
       </c>
       <c r="J34" s="15">
         <f t="shared" si="1"/>
-        <v>450</v>
+        <v>425</v>
       </c>
       <c r="K34" s="16" t="s">
         <v>87</v>
@@ -2485,7 +2488,7 @@
         <v>600</v>
       </c>
       <c r="C35" s="14">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="D35" s="14">
         <v>60</v>
@@ -2504,11 +2507,11 @@
       </c>
       <c r="I35" s="15">
         <f t="shared" si="0"/>
-        <v>1120</v>
+        <v>1160</v>
       </c>
       <c r="J35" s="15">
         <f t="shared" si="1"/>
-        <v>320</v>
+        <v>280</v>
       </c>
       <c r="K35" s="16" t="s">
         <v>56</v>
@@ -2531,7 +2534,7 @@
         <v>420</v>
       </c>
       <c r="C36" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D36" s="14">
         <v>180</v>
@@ -2550,11 +2553,11 @@
       </c>
       <c r="I36" s="15">
         <f t="shared" si="0"/>
-        <v>1050</v>
+        <v>1110</v>
       </c>
       <c r="J36" s="15">
         <f t="shared" si="1"/>
-        <v>390</v>
+        <v>330</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>56</v>
@@ -2577,7 +2580,7 @@
         <v>450</v>
       </c>
       <c r="C37" s="14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D37" s="14">
         <v>120</v>
@@ -2596,11 +2599,11 @@
       </c>
       <c r="I37" s="15">
         <f t="shared" si="0"/>
-        <v>1070</v>
+        <v>1150</v>
       </c>
       <c r="J37" s="15">
         <f t="shared" si="1"/>
-        <v>370</v>
+        <v>290</v>
       </c>
       <c r="K37" s="16" t="s">
         <v>58</v>
@@ -2623,7 +2626,7 @@
         <v>450</v>
       </c>
       <c r="C38" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D38" s="14">
         <v>60</v>
@@ -2642,11 +2645,11 @@
       </c>
       <c r="I38" s="15">
         <f t="shared" si="0"/>
-        <v>1010</v>
+        <v>1060</v>
       </c>
       <c r="J38" s="15">
         <f t="shared" si="1"/>
-        <v>430</v>
+        <v>380</v>
       </c>
       <c r="K38" s="16" t="s">
         <v>56</v>
@@ -2669,7 +2672,7 @@
         <v>300</v>
       </c>
       <c r="C39" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D39" s="14">
         <v>0</v>
@@ -2688,11 +2691,11 @@
       </c>
       <c r="I39" s="15">
         <f t="shared" si="0"/>
-        <v>620</v>
+        <v>670</v>
       </c>
       <c r="J39" s="15">
         <f t="shared" si="1"/>
-        <v>820</v>
+        <v>770</v>
       </c>
       <c r="K39" s="16" t="s">
         <v>58</v>
@@ -2715,7 +2718,7 @@
         <v>400</v>
       </c>
       <c r="C40" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D40" s="14">
         <v>120</v>
@@ -2734,11 +2737,11 @@
       </c>
       <c r="I40" s="15">
         <f t="shared" si="0"/>
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="J40" s="15">
         <f t="shared" si="1"/>
-        <v>720</v>
+        <v>700</v>
       </c>
       <c r="K40" s="16" t="s">
         <v>49</v>
@@ -2761,7 +2764,7 @@
         <v>300</v>
       </c>
       <c r="C41" s="14">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="D41" s="14">
         <v>120</v>
@@ -2780,11 +2783,11 @@
       </c>
       <c r="I41" s="15">
         <f t="shared" si="0"/>
-        <v>660</v>
+        <v>685</v>
       </c>
       <c r="J41" s="15">
         <f t="shared" si="1"/>
-        <v>780</v>
+        <v>755</v>
       </c>
       <c r="K41" s="16" t="s">
         <v>56</v>
@@ -2807,7 +2810,7 @@
         <v>480</v>
       </c>
       <c r="C42" s="14">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="D42" s="14">
         <v>150</v>
@@ -2826,11 +2829,11 @@
       </c>
       <c r="I42" s="15">
         <f t="shared" si="0"/>
-        <v>910</v>
+        <v>955</v>
       </c>
       <c r="J42" s="15">
         <f t="shared" si="1"/>
-        <v>530</v>
+        <v>485</v>
       </c>
       <c r="K42" s="16" t="s">
         <v>49</v>
@@ -2853,7 +2856,7 @@
         <v>300</v>
       </c>
       <c r="C43" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D43" s="14">
         <v>120</v>
@@ -2872,11 +2875,11 @@
       </c>
       <c r="I43" s="15">
         <f t="shared" si="0"/>
-        <v>800</v>
+        <v>830</v>
       </c>
       <c r="J43" s="15">
         <f t="shared" si="1"/>
-        <v>640</v>
+        <v>610</v>
       </c>
       <c r="K43" s="16" t="s">
         <v>49</v>
@@ -2899,7 +2902,7 @@
         <v>420</v>
       </c>
       <c r="C44" s="14">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D44" s="14">
         <v>180</v>
@@ -2918,11 +2921,11 @@
       </c>
       <c r="I44" s="15">
         <f t="shared" si="0"/>
-        <v>1060</v>
+        <v>1150</v>
       </c>
       <c r="J44" s="15">
         <f t="shared" si="1"/>
-        <v>380</v>
+        <v>290</v>
       </c>
       <c r="K44" s="16" t="s">
         <v>49</v>
@@ -2945,7 +2948,7 @@
         <v>420</v>
       </c>
       <c r="C45" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D45" s="14">
         <v>210</v>
@@ -2964,11 +2967,11 @@
       </c>
       <c r="I45" s="15">
         <f t="shared" si="0"/>
-        <v>1000</v>
+        <v>1050</v>
       </c>
       <c r="J45" s="15">
         <f t="shared" si="1"/>
-        <v>440</v>
+        <v>390</v>
       </c>
       <c r="K45" s="16" t="s">
         <v>49</v>
@@ -2991,7 +2994,7 @@
         <v>420</v>
       </c>
       <c r="C46" s="14">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D46" s="14">
         <v>300</v>
@@ -3010,11 +3013,11 @@
       </c>
       <c r="I46" s="15">
         <f t="shared" si="0"/>
-        <v>1080</v>
+        <v>1140</v>
       </c>
       <c r="J46" s="15">
         <f t="shared" si="1"/>
-        <v>360</v>
+        <v>300</v>
       </c>
       <c r="K46" s="16" t="s">
         <v>49</v>
@@ -3037,7 +3040,7 @@
         <v>420</v>
       </c>
       <c r="C47" s="14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="D47" s="14">
         <v>60</v>
@@ -3056,11 +3059,11 @@
       </c>
       <c r="I47" s="15">
         <f t="shared" si="0"/>
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="J47" s="15">
         <f t="shared" si="1"/>
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="K47" s="16" t="s">
         <v>87</v>
@@ -3083,7 +3086,7 @@
         <v>300</v>
       </c>
       <c r="C48" s="14">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="D48" s="14">
         <v>300</v>
@@ -3102,11 +3105,11 @@
       </c>
       <c r="I48" s="15">
         <f t="shared" si="0"/>
-        <v>840</v>
+        <v>850</v>
       </c>
       <c r="J48" s="15">
         <f t="shared" si="1"/>
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="K48" s="16" t="s">
         <v>56</v>
@@ -3129,7 +3132,7 @@
         <v>360</v>
       </c>
       <c r="C49" s="14">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="D49" s="14">
         <v>380</v>
@@ -3148,11 +3151,11 @@
       </c>
       <c r="I49" s="15">
         <f t="shared" si="0"/>
-        <v>940</v>
+        <v>970</v>
       </c>
       <c r="J49" s="15">
         <f>IF(I49="","",1440-I49)</f>
-        <v>500</v>
+        <v>470</v>
       </c>
       <c r="K49" s="16" t="s">
         <v>87</v>
@@ -3175,7 +3178,7 @@
         <v>240</v>
       </c>
       <c r="C50" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D50" s="14">
         <v>60</v>
@@ -3194,11 +3197,11 @@
       </c>
       <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v>820</v>
+        <v>870</v>
       </c>
       <c r="J50" s="15">
         <f>IF(I50="","",1440-I50)</f>
-        <v>620</v>
+        <v>570</v>
       </c>
       <c r="K50" s="16" t="s">
         <v>58</v>
@@ -3221,7 +3224,7 @@
         <v>300</v>
       </c>
       <c r="C51" s="14">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D51" s="14">
         <v>150</v>
@@ -3240,11 +3243,11 @@
       </c>
       <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v>1030</v>
+        <v>1110</v>
       </c>
       <c r="J51" s="15">
         <f>IF(I51="","",1440-I51)</f>
-        <v>410</v>
+        <v>330</v>
       </c>
       <c r="K51" s="16" t="s">
         <v>58</v>
@@ -3260,26 +3263,50 @@
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="13"/>
-      <c r="B52" s="14"/>
-      <c r="C52" s="14"/>
-      <c r="D52" s="14"/>
-      <c r="E52" s="14"/>
-      <c r="F52" s="14"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15" t="str">
+      <c r="A52" s="13">
+        <v>46289</v>
+      </c>
+      <c r="B52" s="14">
+        <v>420</v>
+      </c>
+      <c r="C52" s="14">
+        <v>60</v>
+      </c>
+      <c r="D52" s="14">
+        <v>120</v>
+      </c>
+      <c r="E52" s="14">
+        <v>120</v>
+      </c>
+      <c r="F52" s="14">
+        <v>250</v>
+      </c>
+      <c r="G52" s="14">
+        <v>5</v>
+      </c>
+      <c r="H52" s="14">
+        <v>120</v>
+      </c>
+      <c r="I52" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J52" s="15" t="str">
+        <v>1090</v>
+      </c>
+      <c r="J52" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K52" s="16"/>
-      <c r="L52" s="16"/>
-      <c r="M52" s="16"/>
-      <c r="N52" s="17"/>
+        <v>350</v>
+      </c>
+      <c r="K52" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L52" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M52" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N52" s="17" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A53" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{138E5062-994B-451F-A863-6A1B82B1253B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D672749-5A3E-42D9-A9F0-544CA4F12FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="110">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -364,6 +364,9 @@
   </si>
   <si>
     <t>I have been completing my Python CA2, with my friends</t>
+  </si>
+  <si>
+    <t>Noram day, did some Python coding CA2 and today was good day</t>
   </si>
 </sst>
 </file>
@@ -3309,26 +3312,50 @@
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="13"/>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15" t="str">
+      <c r="A53" s="13">
+        <v>46290</v>
+      </c>
+      <c r="B53" s="14">
+        <v>300</v>
+      </c>
+      <c r="C53" s="14">
+        <v>100</v>
+      </c>
+      <c r="D53" s="14">
+        <v>0</v>
+      </c>
+      <c r="E53" s="14">
+        <v>240</v>
+      </c>
+      <c r="F53" s="14">
+        <v>300</v>
+      </c>
+      <c r="G53" s="14">
+        <v>6</v>
+      </c>
+      <c r="H53" s="14">
+        <v>100</v>
+      </c>
+      <c r="I53" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J53" s="15" t="str">
+        <v>1040</v>
+      </c>
+      <c r="J53" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K53" s="16"/>
-      <c r="L53" s="16"/>
-      <c r="M53" s="16"/>
-      <c r="N53" s="17"/>
+        <v>400</v>
+      </c>
+      <c r="K53" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L53" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M53" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N53" s="17" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A54" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D672749-5A3E-42D9-A9F0-544CA4F12FFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD134B2-06F9-4326-8368-347D3707FBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="111">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -367,6 +367,9 @@
   </si>
   <si>
     <t>Noram day, did some Python coding CA2 and today was good day</t>
+  </si>
+  <si>
+    <t>Python CA2 code is almost completed,did some improvement in my code</t>
   </si>
 </sst>
 </file>
@@ -3357,27 +3360,51 @@
         <v>109</v>
       </c>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="13"/>
-      <c r="B54" s="14"/>
-      <c r="C54" s="14"/>
-      <c r="D54" s="14"/>
-      <c r="E54" s="14"/>
-      <c r="F54" s="14"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15" t="str">
+    <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A54" s="13">
+        <v>46291</v>
+      </c>
+      <c r="B54" s="14">
+        <v>360</v>
+      </c>
+      <c r="C54" s="14">
+        <v>120</v>
+      </c>
+      <c r="D54" s="14">
+        <v>0</v>
+      </c>
+      <c r="E54" s="14">
+        <v>300</v>
+      </c>
+      <c r="F54" s="14">
+        <v>250</v>
+      </c>
+      <c r="G54" s="14">
+        <v>5</v>
+      </c>
+      <c r="H54" s="14">
+        <v>100</v>
+      </c>
+      <c r="I54" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J54" s="15" t="str">
+        <v>1130</v>
+      </c>
+      <c r="J54" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K54" s="16"/>
-      <c r="L54" s="16"/>
-      <c r="M54" s="16"/>
-      <c r="N54" s="17"/>
+        <v>310</v>
+      </c>
+      <c r="K54" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L54" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M54" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N54" s="17" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A55" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2FD134B2-06F9-4326-8368-347D3707FBF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578D4D23-E739-4286-A429-9E22DC7C1BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -369,7 +369,13 @@
     <t>Noram day, did some Python coding CA2 and today was good day</t>
   </si>
   <si>
-    <t>Python CA2 code is almost completed,did some improvement in my code</t>
+    <t>Python CA2 code is almost completed,did some improvement in my code,Protest has happened today, Every thing is destroyed</t>
+  </si>
+  <si>
+    <t>Main gate had been broken and ousiders attacked, situation is very bad today</t>
+  </si>
+  <si>
+    <t>Days are not going well</t>
   </si>
 </sst>
 </file>
@@ -3394,61 +3400,107 @@
         <v>310</v>
       </c>
       <c r="K54" s="16" t="s">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="L54" s="16" t="s">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="M54" s="16" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="N54" s="17" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="13"/>
-      <c r="B55" s="14"/>
-      <c r="C55" s="14"/>
-      <c r="D55" s="14"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="14"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15" t="str">
+    <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A55" s="13">
+        <v>46292</v>
+      </c>
+      <c r="B55" s="14">
+        <v>180</v>
+      </c>
+      <c r="C55" s="14">
+        <v>60</v>
+      </c>
+      <c r="D55" s="14">
+        <v>100</v>
+      </c>
+      <c r="E55" s="14">
+        <v>250</v>
+      </c>
+      <c r="F55" s="14">
+        <v>250</v>
+      </c>
+      <c r="G55" s="14">
+        <v>5</v>
+      </c>
+      <c r="H55" s="14">
+        <v>180</v>
+      </c>
+      <c r="I55" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J55" s="15" t="str">
+        <v>1020</v>
+      </c>
+      <c r="J55" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K55" s="16"/>
-      <c r="L55" s="16"/>
-      <c r="M55" s="16"/>
-      <c r="N55" s="17"/>
+        <v>420</v>
+      </c>
+      <c r="K55" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L55" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M55" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="N55" s="17" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="13"/>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15" t="str">
+      <c r="A56" s="13">
+        <v>46293</v>
+      </c>
+      <c r="B56" s="14">
+        <v>240</v>
+      </c>
+      <c r="C56" s="14">
+        <v>20</v>
+      </c>
+      <c r="D56" s="14">
+        <v>60</v>
+      </c>
+      <c r="E56" s="14">
+        <v>20</v>
+      </c>
+      <c r="F56" s="14">
+        <v>0</v>
+      </c>
+      <c r="G56" s="14">
+        <v>0</v>
+      </c>
+      <c r="H56" s="14">
+        <v>200</v>
+      </c>
+      <c r="I56" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J56" s="15" t="str">
+        <v>540</v>
+      </c>
+      <c r="J56" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K56" s="16"/>
-      <c r="L56" s="16"/>
+        <v>900</v>
+      </c>
+      <c r="K56" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="L56" s="16" t="s">
+        <v>69</v>
+      </c>
       <c r="M56" s="16"/>
-      <c r="N56" s="17"/>
+      <c r="N56" s="17" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A57" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{578D4D23-E739-4286-A429-9E22DC7C1BBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594FAC2A-3D0E-4343-AF9E-FE70DDC2CD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="113">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -3497,7 +3497,9 @@
       <c r="L56" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="M56" s="16"/>
+      <c r="M56" s="16" t="s">
+        <v>51</v>
+      </c>
       <c r="N56" s="17" t="s">
         <v>112</v>
       </c>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{594FAC2A-3D0E-4343-AF9E-FE70DDC2CD84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8779EA7-A741-4EB8-BFAB-B3EE182B7CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="115">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -162,9 +162,6 @@
     <t>Class (min)</t>
   </si>
   <si>
-    <t>Classes Attended</t>
-  </si>
-  <si>
     <t>Other Activities (min)</t>
   </si>
   <si>
@@ -376,6 +373,15 @@
   </si>
   <si>
     <t>Days are not going well</t>
+  </si>
+  <si>
+    <t>Going home, Travelled in the bus for 10 hours I was so tired</t>
+  </si>
+  <si>
+    <t>Did't found any direct bus to home, waited 12 hours for the bus on bus station and travelled 12 hours</t>
+  </si>
+  <si>
+    <t>Finally I got home and I slept very well today finally travelling is over now I can rest a bit</t>
   </si>
 </sst>
 </file>
@@ -993,7 +999,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A33" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.3">
@@ -1067,7 +1073,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C2" s="20"/>
       <c r="D2" s="20"/>
@@ -1084,7 +1090,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C3" s="20"/>
       <c r="D3" s="20"/>
@@ -1092,7 +1098,7 @@
         <v>33</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G3" s="20"/>
     </row>
@@ -1133,29 +1139,29 @@
       <c r="F5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="G5" s="7">
+        <v>0</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="K5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="M5" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="M5" s="7" t="s">
+      <c r="N5" s="7" t="s">
         <v>47</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1192,16 +1198,16 @@
         <v>555</v>
       </c>
       <c r="K6" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="L6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L6" s="11" t="s">
+      <c r="M6" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="11" t="s">
+      <c r="N6" s="12" t="s">
         <v>51</v>
-      </c>
-      <c r="N6" s="12" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
@@ -1238,16 +1244,16 @@
         <v>600</v>
       </c>
       <c r="K7" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L7" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="17" t="s">
         <v>56</v>
-      </c>
-      <c r="M7" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1284,16 +1290,16 @@
         <v>525</v>
       </c>
       <c r="K8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="L8" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8" s="17" t="s">
         <v>58</v>
-      </c>
-      <c r="L8" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -1330,16 +1336,16 @@
         <v>340</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L9" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M9" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.3">
@@ -1376,16 +1382,16 @@
         <v>360</v>
       </c>
       <c r="K10" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L10" s="16" t="s">
+      <c r="M10" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N10" s="17" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.3">
@@ -1422,16 +1428,16 @@
         <v>450</v>
       </c>
       <c r="K11" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L11" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M11" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N11" s="17" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.3">
@@ -1468,16 +1474,16 @@
         <v>380</v>
       </c>
       <c r="K12" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L12" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L12" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="M12" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12" s="17" t="s">
         <v>64</v>
-      </c>
-      <c r="N12" s="17" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1514,16 +1520,16 @@
         <v>470</v>
       </c>
       <c r="K13" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L13" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L13" s="16" t="s">
+      <c r="M13" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M13" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N13" s="17" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1560,16 +1566,16 @@
         <v>660</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L14" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M14" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M14" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N14" s="17" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1606,16 +1612,16 @@
         <v>340</v>
       </c>
       <c r="K15" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L15" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M15" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N15" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.3">
@@ -1652,16 +1658,16 @@
         <v>410</v>
       </c>
       <c r="K16" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L16" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M16" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N16" s="17" t="s">
         <v>69</v>
-      </c>
-      <c r="M16" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N16" s="17" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.3">
@@ -1698,16 +1704,16 @@
         <v>500</v>
       </c>
       <c r="K17" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L17" s="16" t="s">
+      <c r="M17" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M17" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N17" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1744,16 +1750,16 @@
         <v>435</v>
       </c>
       <c r="K18" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L18" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L18" s="16" t="s">
+      <c r="M18" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M18" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N18" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.3">
@@ -1790,16 +1796,16 @@
         <v>520</v>
       </c>
       <c r="K19" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L19" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L19" s="16" t="s">
+      <c r="M19" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M19" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N19" s="17" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.3">
@@ -1836,16 +1842,16 @@
         <v>550</v>
       </c>
       <c r="K20" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L20" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M20" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="21" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1882,16 +1888,16 @@
         <v>375</v>
       </c>
       <c r="K21" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L21" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L21" s="16" t="s">
+      <c r="M21" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M21" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N21" s="17" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.3">
@@ -1928,16 +1934,16 @@
         <v>485</v>
       </c>
       <c r="K22" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L22" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M22" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N22" s="17" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -1974,16 +1980,16 @@
         <v>460</v>
       </c>
       <c r="K23" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L23" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M23" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N23" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.3">
@@ -2020,16 +2026,16 @@
         <v>335</v>
       </c>
       <c r="K24" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="L24" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M24" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N24" s="17" t="s">
         <v>77</v>
-      </c>
-      <c r="L24" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="M24" s="16" t="s">
-        <v>51</v>
-      </c>
-      <c r="N24" s="17" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.3">
@@ -2066,16 +2072,16 @@
         <v>540</v>
       </c>
       <c r="K25" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L25" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M25" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N25" s="17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.3">
@@ -2112,16 +2118,16 @@
         <v>505</v>
       </c>
       <c r="K26" s="16" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="L26" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M26" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M26" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N26" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.3">
@@ -2158,16 +2164,16 @@
         <v>540</v>
       </c>
       <c r="K27" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L27" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L27" s="16" t="s">
+      <c r="M27" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M27" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N27" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.3">
@@ -2204,16 +2210,16 @@
         <v>520</v>
       </c>
       <c r="K28" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L28" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M28" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N28" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.3">
@@ -2250,16 +2256,16 @@
         <v>590</v>
       </c>
       <c r="K29" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L29" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L29" s="16" t="s">
+      <c r="M29" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M29" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N29" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2296,16 +2302,16 @@
         <v>410</v>
       </c>
       <c r="K30" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L30" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M30" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N30" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.3">
@@ -2342,16 +2348,16 @@
         <v>430</v>
       </c>
       <c r="K31" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L31" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L31" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="M31" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N31" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.3">
@@ -2388,16 +2394,16 @@
         <v>320</v>
       </c>
       <c r="K32" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L32" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M32" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N32" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2434,16 +2440,16 @@
         <v>460</v>
       </c>
       <c r="K33" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L33" s="16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M33" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N33" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2480,16 +2486,16 @@
         <v>425</v>
       </c>
       <c r="K34" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L34" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="L34" s="16" t="s">
+      <c r="M34" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N34" s="17" t="s">
         <v>88</v>
-      </c>
-      <c r="M34" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N34" s="17" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="35" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2526,16 +2532,16 @@
         <v>280</v>
       </c>
       <c r="K35" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L35" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M35" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M35" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N35" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2572,16 +2578,16 @@
         <v>330</v>
       </c>
       <c r="K36" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L36" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M36" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N36" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="37" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2618,16 +2624,16 @@
         <v>290</v>
       </c>
       <c r="K37" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L37" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M37" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N37" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.3">
@@ -2664,16 +2670,16 @@
         <v>380</v>
       </c>
       <c r="K38" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L38" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M38" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N38" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.3">
@@ -2710,16 +2716,16 @@
         <v>770</v>
       </c>
       <c r="K39" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L39" s="16" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M39" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N39" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.3">
@@ -2756,16 +2762,16 @@
         <v>700</v>
       </c>
       <c r="K40" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L40" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L40" s="16" t="s">
+      <c r="M40" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M40" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N40" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.3">
@@ -2802,16 +2808,16 @@
         <v>755</v>
       </c>
       <c r="K41" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L41" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M41" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M41" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N41" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2848,16 +2854,16 @@
         <v>485</v>
       </c>
       <c r="K42" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L42" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M42" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N42" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="43" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -2894,16 +2900,16 @@
         <v>610</v>
       </c>
       <c r="K43" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L43" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M43" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N43" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44" spans="1:14" ht="43.2" x14ac:dyDescent="0.3">
@@ -2940,16 +2946,16 @@
         <v>290</v>
       </c>
       <c r="K44" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L44" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L44" s="16" t="s">
-        <v>50</v>
-      </c>
       <c r="M44" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N44" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.3">
@@ -2986,16 +2992,16 @@
         <v>390</v>
       </c>
       <c r="K45" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L45" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L45" s="16" t="s">
+      <c r="M45" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M45" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N45" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.3">
@@ -3032,16 +3038,16 @@
         <v>300</v>
       </c>
       <c r="K46" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L46" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L46" s="16" t="s">
+      <c r="M46" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M46" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N46" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.3">
@@ -3078,16 +3084,16 @@
         <v>590</v>
       </c>
       <c r="K47" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L47" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="L47" s="16" t="s">
-        <v>88</v>
-      </c>
       <c r="M47" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N47" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.3">
@@ -3124,16 +3130,16 @@
         <v>590</v>
       </c>
       <c r="K48" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="L48" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M48" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M48" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N48" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
@@ -3170,16 +3176,16 @@
         <v>470</v>
       </c>
       <c r="K49" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L49" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="M49" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N49" s="17" t="s">
         <v>104</v>
-      </c>
-      <c r="M49" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="N49" s="17" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3216,16 +3222,16 @@
         <v>570</v>
       </c>
       <c r="K50" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L50" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M50" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N50" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3262,16 +3268,16 @@
         <v>330</v>
       </c>
       <c r="K51" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L51" s="16" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M51" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N51" s="17" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
@@ -3308,16 +3314,16 @@
         <v>350</v>
       </c>
       <c r="K52" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L52" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L52" s="16" t="s">
+      <c r="M52" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M52" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N52" s="17" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
@@ -3354,16 +3360,16 @@
         <v>400</v>
       </c>
       <c r="K53" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L53" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="L53" s="16" t="s">
+      <c r="M53" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M53" s="16" t="s">
-        <v>51</v>
-      </c>
       <c r="N53" s="17" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3400,16 +3406,16 @@
         <v>310</v>
       </c>
       <c r="K54" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L54" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="L54" s="16" t="s">
-        <v>88</v>
-      </c>
       <c r="M54" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N54" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="55" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3446,16 +3452,16 @@
         <v>420</v>
       </c>
       <c r="K55" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L55" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="L55" s="16" t="s">
-        <v>88</v>
-      </c>
       <c r="M55" s="16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N55" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
@@ -3492,83 +3498,155 @@
         <v>900</v>
       </c>
       <c r="K56" s="16" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="L56" s="16" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M56" s="16" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="N56" s="17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A57" s="13">
+        <v>46294</v>
+      </c>
+      <c r="B57" s="14">
+        <v>180</v>
+      </c>
+      <c r="C57" s="14">
+        <v>200</v>
+      </c>
+      <c r="D57" s="14">
+        <v>0</v>
+      </c>
+      <c r="E57" s="14">
+        <v>0</v>
+      </c>
+      <c r="F57" s="14">
+        <v>0</v>
+      </c>
+      <c r="G57" s="14">
+        <v>0</v>
+      </c>
+      <c r="H57" s="14">
+        <v>1060</v>
+      </c>
+      <c r="I57" s="15">
+        <f t="shared" si="0"/>
+        <v>1440</v>
+      </c>
+      <c r="J57" s="15">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="K57" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L57" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M57" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N57" s="17" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="13"/>
-      <c r="B57" s="14"/>
-      <c r="C57" s="14"/>
-      <c r="D57" s="14"/>
-      <c r="E57" s="14"/>
-      <c r="F57" s="14"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15" t="str">
+    <row r="58" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A58" s="13">
+        <v>46295</v>
+      </c>
+      <c r="B58" s="14">
+        <v>240</v>
+      </c>
+      <c r="C58" s="14">
+        <v>350</v>
+      </c>
+      <c r="D58" s="14">
+        <v>0</v>
+      </c>
+      <c r="E58" s="14">
+        <v>0</v>
+      </c>
+      <c r="F58" s="14">
+        <v>0</v>
+      </c>
+      <c r="G58" s="14">
+        <v>0</v>
+      </c>
+      <c r="H58" s="14">
+        <v>850</v>
+      </c>
+      <c r="I58" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J57" s="15" t="str">
+        <v>1440</v>
+      </c>
+      <c r="J58" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K57" s="16"/>
-      <c r="L57" s="16"/>
-      <c r="M57" s="16"/>
-      <c r="N57" s="17"/>
-    </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="13"/>
-      <c r="B58" s="14"/>
-      <c r="C58" s="14"/>
-      <c r="D58" s="14"/>
-      <c r="E58" s="14"/>
-      <c r="F58" s="14"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15" t="str">
+        <v>0</v>
+      </c>
+      <c r="K58" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="L58" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="M58" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N58" s="17" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A59" s="13">
+        <v>46296</v>
+      </c>
+      <c r="B59" s="14">
+        <v>540</v>
+      </c>
+      <c r="C59" s="14">
+        <v>100</v>
+      </c>
+      <c r="D59" s="14">
+        <v>0</v>
+      </c>
+      <c r="E59" s="14">
+        <v>0</v>
+      </c>
+      <c r="F59" s="14">
+        <v>0</v>
+      </c>
+      <c r="G59" s="14">
+        <v>0</v>
+      </c>
+      <c r="H59" s="14">
+        <v>240</v>
+      </c>
+      <c r="I59" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J58" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J59" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K58" s="16"/>
-      <c r="L58" s="16"/>
-      <c r="M58" s="16"/>
-      <c r="N58" s="17"/>
-    </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A59" s="13"/>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15" t="str">
-        <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J59" s="15" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K59" s="16"/>
-      <c r="L59" s="16"/>
-      <c r="M59" s="16"/>
-      <c r="N59" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K59" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L59" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M59" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="N59" s="17" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A60" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8779EA7-A741-4EB8-BFAB-B3EE182B7CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726AC81F-B875-41AE-AE8E-AFCEE6F68319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -381,7 +381,7 @@
     <t>Did't found any direct bus to home, waited 12 hours for the bus on bus station and travelled 12 hours</t>
   </si>
   <si>
-    <t>Finally I got home and I slept very well today finally travelling is over now I can rest a bit</t>
+    <t>Finally I got home and I slept very well today finally travelling is over now I can rest a bit.</t>
   </si>
 </sst>
 </file>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{726AC81F-B875-41AE-AE8E-AFCEE6F68319}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB6E212-22B7-4FC9-841F-01DD6F61CCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -378,10 +378,10 @@
     <t>Going home, Travelled in the bus for 10 hours I was so tired</t>
   </si>
   <si>
-    <t>Did't found any direct bus to home, waited 12 hours for the bus on bus station and travelled 12 hours</t>
-  </si>
-  <si>
     <t>Finally I got home and I slept very well today finally travelling is over now I can rest a bit.</t>
+  </si>
+  <si>
+    <t>Did't found any direct bus to home, waited 12 hours for the bus on bus station and travelled 12 hours.</t>
   </si>
 </sst>
 </file>
@@ -3599,7 +3599,7 @@
         <v>57</v>
       </c>
       <c r="N58" s="17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="59" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
@@ -3645,7 +3645,7 @@
         <v>57</v>
       </c>
       <c r="N59" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB6E212-22B7-4FC9-841F-01DD6F61CCB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E428AB4A-67C8-414E-876E-EC64E4E36B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="117">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -382,6 +382,12 @@
   </si>
   <si>
     <t>Did't found any direct bus to home, waited 12 hours for the bus on bus station and travelled 12 hours.</t>
+  </si>
+  <si>
+    <t>Classes Attended</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Normal day </t>
   </si>
 </sst>
 </file>
@@ -1139,8 +1145,8 @@
       <c r="F5" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="G5" s="7">
-        <v>0</v>
+      <c r="G5" s="7" t="s">
+        <v>115</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>41</v>
@@ -3649,26 +3655,50 @@
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="13"/>
-      <c r="B60" s="14"/>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15" t="str">
+      <c r="A60" s="13">
+        <v>46297</v>
+      </c>
+      <c r="B60" s="14">
+        <v>360</v>
+      </c>
+      <c r="C60" s="14">
+        <v>10</v>
+      </c>
+      <c r="D60" s="14">
+        <v>180</v>
+      </c>
+      <c r="E60" s="14">
+        <v>0</v>
+      </c>
+      <c r="F60" s="14">
+        <v>0</v>
+      </c>
+      <c r="G60" s="14">
+        <v>0</v>
+      </c>
+      <c r="H60" s="14">
+        <v>240</v>
+      </c>
+      <c r="I60" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J60" s="15" t="str">
+        <v>790</v>
+      </c>
+      <c r="J60" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K60" s="16"/>
-      <c r="L60" s="16"/>
-      <c r="M60" s="16"/>
-      <c r="N60" s="17"/>
+        <v>650</v>
+      </c>
+      <c r="K60" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L60" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="M60" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N60" s="17" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A61" s="13"/>

--- a/my_daily_data.xlsx
+++ b/my_daily_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MCA - LPU\Semester 1\code.py\My_daily_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E428AB4A-67C8-414E-876E-EC64E4E36B83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D7D7C54-ED96-4F39-B6EB-B0C3D10618DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="1935" windowWidth="20730" windowHeight="11040" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -18,17 +18,6 @@
   </sheets>
   <calcPr calcId="191028" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -37,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="273" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="118">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -388,6 +377,9 @@
   </si>
   <si>
     <t xml:space="preserve">Normal day </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Infection in my eyes and dryness </t>
   </si>
 </sst>
 </file>
@@ -3701,26 +3693,50 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="13"/>
-      <c r="B61" s="14"/>
-      <c r="C61" s="14"/>
-      <c r="D61" s="14"/>
-      <c r="E61" s="14"/>
-      <c r="F61" s="14"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15" t="str">
+      <c r="A61" s="13">
+        <v>46298</v>
+      </c>
+      <c r="B61" s="14">
+        <v>380</v>
+      </c>
+      <c r="C61" s="14">
+        <v>20</v>
+      </c>
+      <c r="D61" s="14">
+        <v>120</v>
+      </c>
+      <c r="E61" s="14">
+        <v>60</v>
+      </c>
+      <c r="F61" s="14">
+        <v>0</v>
+      </c>
+      <c r="G61" s="14">
+        <v>0</v>
+      </c>
+      <c r="H61" s="14">
+        <v>300</v>
+      </c>
+      <c r="I61" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J61" s="15" t="str">
+        <v>880</v>
+      </c>
+      <c r="J61" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K61" s="16"/>
-      <c r="L61" s="16"/>
-      <c r="M61" s="16"/>
-      <c r="N61" s="17"/>
+        <v>560</v>
+      </c>
+      <c r="K61" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="L61" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="M61" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="N61" s="17" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A62" s="13"/>
